--- a/artfynd/A 26985-2025 artfynd.xlsx
+++ b/artfynd/A 26985-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1006,6 +1006,120 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125999557</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91247</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 26985, Frösvi, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>575239</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6403965</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Blackstad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp lågt i sned tall</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26985-2025 artfynd.xlsx
+++ b/artfynd/A 26985-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>125999557</v>
       </c>
       <c r="B5" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26985-2025 artfynd.xlsx
+++ b/artfynd/A 26985-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>125999557</v>
       </c>
       <c r="B5" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26985-2025 artfynd.xlsx
+++ b/artfynd/A 26985-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125851209</v>
       </c>
       <c r="B2" t="n">
-        <v>57809</v>
+        <v>57810</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>125851123</v>
       </c>
       <c r="B3" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>125898558</v>
       </c>
       <c r="B4" t="n">
-        <v>57645</v>
+        <v>57646</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>125999557</v>
       </c>
       <c r="B5" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26985-2025 artfynd.xlsx
+++ b/artfynd/A 26985-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>125999557</v>
       </c>
       <c r="B5" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26985-2025 artfynd.xlsx
+++ b/artfynd/A 26985-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>125999557</v>
       </c>
       <c r="B5" t="n">
-        <v>91256</v>
+        <v>91258</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26985-2025 artfynd.xlsx
+++ b/artfynd/A 26985-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125851209</v>
       </c>
       <c r="B2" t="n">
-        <v>57810</v>
+        <v>57814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>125851123</v>
       </c>
       <c r="B3" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>125898558</v>
       </c>
       <c r="B4" t="n">
-        <v>57646</v>
+        <v>57650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>125999557</v>
       </c>
       <c r="B5" t="n">
-        <v>91258</v>
+        <v>91262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 26985-2025 artfynd.xlsx
+++ b/artfynd/A 26985-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125851209</v>
       </c>
       <c r="B2" t="n">
-        <v>57814</v>
+        <v>57815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>125851123</v>
       </c>
       <c r="B3" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>125898558</v>
       </c>
       <c r="B4" t="n">
-        <v>57650</v>
+        <v>57651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>125999557</v>
       </c>
       <c r="B5" t="n">
-        <v>91262</v>
+        <v>91265</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
